--- a/news_daily/2026-09-02.xlsx
+++ b/news_daily/2026-09-02.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -1264,28 +1264,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1325,7 +1329,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1334,7 +1338,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>a678c198f00e4dd59c349b2df8d484b1</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>a07bf015c59d33137be882fc</t>
@@ -1355,7 +1363,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1399,10 +1411,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1438,28 +1462,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1499,7 +1527,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1508,7 +1536,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>dc63b1c0de854b3db558eb97e3773914</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>7263e7b0fa53b887df1fb86a</t>
@@ -1529,7 +1561,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1573,10 +1609,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -4065,170 +4113,194 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>WY</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Weyerhaeuser</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>2026-09-02T21:32:00+08:00</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Homeowners who lost property in massive Highway 229 landslide sue Weyerhaeuser in federal court</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>'-0.878</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNSUFmcTJvcXNjb0FuT1JPMUNWNU0tazdpX1h5Tm9ITWRVRXFCdmVfTUpmb1FVNnJDX19FWk80QWtTclo4SEJLdWgwNEhTUUhqaTRqZVBET1NBMEJ3OEV3S3NEdTBjb196ZjJRWTRGVWlLa3B5WV9DejFvYWFLZEZoSFIta2ZCZUhnS0Zpd3ZkemRBeGhrSWJwSUFKM1BSRXJVbU1NczZQeHcyT2xKNlE4cmI4VUp1U1BhbWMyZ2duNzdCNFY1N1FBa2NObWxvQXNudnVWSV9jaC1VTVA1bi1MWg?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>NPR for Oregonians</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr"/>
+      <c r="X19" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>1fed1bf0b1724ebb8f24bbef97648bd6</t>
+        </is>
+      </c>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>8980a06dfde0c90b9e2a6380</t>
+        </is>
+      </c>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>fd2da2a49aa71549e38eba16</t>
+        </is>
+      </c>
+      <c r="AE19" s="4" t="inlineStr"/>
+      <c r="AF19" s="4" t="inlineStr"/>
+      <c r="AG19" s="4" t="inlineStr"/>
+      <c r="AH19" s="4" t="inlineStr"/>
+      <c r="AI19" s="4" t="inlineStr"/>
+      <c r="AJ19" s="4" t="inlineStr"/>
+      <c r="AK19" s="4" t="inlineStr"/>
+      <c r="AL19" s="4" t="inlineStr"/>
+      <c r="AM19" s="4" t="inlineStr"/>
+      <c r="AN19" s="4" t="inlineStr"/>
+      <c r="AO19" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>'-0.878</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNSUFmcTJvcXNjb0FuT1JPMUNWNU0tazdpX1h5Tm9ITWRVRXFCdmVfTUpmb1FVNnJDX19FWk80QWtTclo4SEJLdWgwNEhTUUhqaTRqZVBET1NBMEJ3OEV3S3NEdTBjb196ZjJRWTRGVWlLa3B5WV9DejFvYWFLZEZoSFIta2ZCZUhnS0Zpd3ZkemRBeGhrSWJwSUFKM1BSRXJVbU1NczZQeHcyT2xKNlE4cmI4VUp1U1BhbWMyZ2duNzdCNFY1N1FBa2NObWxvQXNudnVWSV9jaC1VTVA1bi1MWg?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>NPR for Oregonians</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr"/>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>landslide</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>8980a06dfde0c90b9e2a6380</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>fd2da2a49aa71549e38eba16</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="inlineStr"/>
-      <c r="AF19" s="2" t="inlineStr"/>
-      <c r="AG19" s="2" t="inlineStr"/>
-      <c r="AH19" s="2" t="inlineStr"/>
-      <c r="AI19" s="2" t="inlineStr"/>
-      <c r="AJ19" s="2" t="inlineStr"/>
-      <c r="AK19" s="2" t="inlineStr"/>
-      <c r="AL19" s="2" t="inlineStr"/>
-      <c r="AM19" s="2" t="inlineStr"/>
-      <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
-      <c r="AP19" s="2" t="inlineStr"/>
-      <c r="AQ19" s="2" t="inlineStr"/>
-      <c r="AR19" s="2" t="inlineStr"/>
-      <c r="AS19" s="2" t="inlineStr"/>
-      <c r="AT19" s="2" t="inlineStr"/>
-      <c r="AU19" s="2" t="inlineStr"/>
-      <c r="AV19" s="2" t="inlineStr"/>
-      <c r="AW19" s="2" t="inlineStr"/>
-      <c r="AX19" s="2" t="inlineStr"/>
-      <c r="AY19" s="2" t="inlineStr"/>
-      <c r="AZ19" s="2" t="inlineStr"/>
-      <c r="BA19" s="2" t="inlineStr"/>
-      <c r="BB19" s="2" t="inlineStr">
+      <c r="AP19" s="4" t="inlineStr"/>
+      <c r="AQ19" s="4" t="inlineStr"/>
+      <c r="AR19" s="4" t="inlineStr"/>
+      <c r="AS19" s="4" t="inlineStr"/>
+      <c r="AT19" s="4" t="inlineStr"/>
+      <c r="AU19" s="4" t="inlineStr"/>
+      <c r="AV19" s="4" t="inlineStr"/>
+      <c r="AW19" s="4" t="inlineStr"/>
+      <c r="AX19" s="4" t="inlineStr"/>
+      <c r="AY19" s="4" t="inlineStr"/>
+      <c r="AZ19" s="4" t="inlineStr"/>
+      <c r="BA19" s="4" t="inlineStr"/>
+      <c r="BB19" s="4" t="inlineStr">
         <is>
           <t>WY</t>
         </is>
       </c>
-      <c r="BC19" s="2" t="inlineStr">
+      <c r="BC19" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="2" t="inlineStr"/>
-      <c r="BE19" s="2" t="inlineStr">
+      <c r="BD19" s="4" t="inlineStr"/>
+      <c r="BE19" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF19" s="2" t="inlineStr"/>
-      <c r="BG19" s="2" t="inlineStr">
+      <c r="BF19" s="4" t="inlineStr"/>
+      <c r="BG19" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
-      <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BH19" s="4" t="inlineStr"/>
+      <c r="BI19" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4442,28 +4514,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4503,7 +4579,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4512,7 +4588,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>b618ff8796a94d97b11c0719921555fd</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>458d8b5234bdf104cc55918e</t>
@@ -4533,7 +4613,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4569,10 +4653,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4988,28 +5084,32 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5049,7 +5149,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -5058,7 +5158,11 @@
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>5d26adf55270429d881fbde404f0462a</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>48865ce892701484d73379ed</t>
@@ -5079,7 +5183,11 @@
       <c r="AL24" s="2" t="inlineStr"/>
       <c r="AM24" s="2" t="inlineStr"/>
       <c r="AN24" s="2" t="inlineStr"/>
-      <c r="AO24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="2" t="inlineStr"/>
       <c r="AQ24" s="2" t="inlineStr"/>
       <c r="AR24" s="2" t="inlineStr"/>
@@ -5123,10 +5231,22 @@
         </is>
       </c>
       <c r="BH24" s="2" t="inlineStr"/>
-      <c r="BI24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ24" s="2" t="inlineStr"/>
-      <c r="BK24" s="2" t="inlineStr"/>
-      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5162,28 +5282,32 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5223,7 +5347,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -5232,7 +5356,11 @@
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr"/>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>17fb8ec7000044c1b5fc1262dfd5a4b1</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>573e27be1710f12a6430a5bc</t>
@@ -5253,7 +5381,11 @@
       <c r="AL25" s="2" t="inlineStr"/>
       <c r="AM25" s="2" t="inlineStr"/>
       <c r="AN25" s="2" t="inlineStr"/>
-      <c r="AO25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP25" s="2" t="inlineStr"/>
       <c r="AQ25" s="2" t="inlineStr"/>
       <c r="AR25" s="2" t="inlineStr"/>
@@ -5297,10 +5429,22 @@
         </is>
       </c>
       <c r="BH25" s="2" t="inlineStr"/>
-      <c r="BI25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ25" s="2" t="inlineStr"/>
-      <c r="BK25" s="2" t="inlineStr"/>
-      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5336,28 +5480,32 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5397,7 +5545,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5406,7 +5554,11 @@
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>b08ab672eebc40ccbf105ee3350e693d</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>29dcf09ac40a4122dd49bf14</t>
@@ -5427,7 +5579,11 @@
       <c r="AL26" s="2" t="inlineStr"/>
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr"/>
-      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="2" t="inlineStr"/>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="inlineStr"/>
@@ -5471,10 +5627,22 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
-      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="2" t="inlineStr"/>
-      <c r="BK26" s="2" t="inlineStr"/>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5510,28 +5678,32 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5571,7 +5743,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -5580,7 +5752,11 @@
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr"/>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>77c95cad0eac4fc3a3e053346318d64f</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>1315b814518f8f957b46edfe</t>
@@ -5601,7 +5777,11 @@
       <c r="AL27" s="2" t="inlineStr"/>
       <c r="AM27" s="2" t="inlineStr"/>
       <c r="AN27" s="2" t="inlineStr"/>
-      <c r="AO27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="2" t="inlineStr"/>
       <c r="AQ27" s="2" t="inlineStr"/>
       <c r="AR27" s="2" t="inlineStr"/>
@@ -5637,10 +5817,22 @@
         </is>
       </c>
       <c r="BH27" s="2" t="inlineStr"/>
-      <c r="BI27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ27" s="2" t="inlineStr"/>
-      <c r="BK27" s="2" t="inlineStr"/>
-      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -7014,28 +7206,32 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7075,7 +7271,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -7084,7 +7280,11 @@
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr"/>
-      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>dbe336ced12445fe9f8d4a6e8d43efe7</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>48de785883fd646102f0ba5a</t>
@@ -7105,7 +7305,11 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
-      <c r="AO35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="2" t="inlineStr"/>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
@@ -7149,10 +7353,22 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
-      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ35" s="2" t="inlineStr"/>
-      <c r="BK35" s="2" t="inlineStr"/>
-      <c r="BL35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7382,28 +7598,32 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7443,7 +7663,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -7452,7 +7672,11 @@
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr"/>
-      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>fce6d0f114c3403cb0887c21b4ea2fec</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>060adaab5ab1e9cd9d4ecce9</t>
@@ -7473,7 +7697,11 @@
       <c r="AL37" s="2" t="inlineStr"/>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
-      <c r="AO37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="2" t="inlineStr"/>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -7517,10 +7745,22 @@
         </is>
       </c>
       <c r="BH37" s="2" t="inlineStr"/>
-      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="2" t="inlineStr"/>
-      <c r="BK37" s="2" t="inlineStr"/>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -7944,28 +8184,32 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -8005,7 +8249,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -8014,7 +8258,11 @@
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr"/>
-      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>63dc34f3df9d4276a1c8de09f332aaae</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>03cee8690ba26fd604c7a6db</t>
@@ -8035,7 +8283,11 @@
       <c r="AL40" s="2" t="inlineStr"/>
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr"/>
-      <c r="AO40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP40" s="2" t="inlineStr"/>
       <c r="AQ40" s="2" t="inlineStr"/>
       <c r="AR40" s="2" t="inlineStr"/>
@@ -8079,10 +8331,22 @@
         </is>
       </c>
       <c r="BH40" s="2" t="inlineStr"/>
-      <c r="BI40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ40" s="2" t="inlineStr"/>
-      <c r="BK40" s="2" t="inlineStr"/>
-      <c r="BL40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8118,28 +8382,32 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -8179,7 +8447,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -8188,7 +8456,11 @@
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr"/>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>d4910049bc46464081967b92b4eeea64</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>18fc8c1a3f7ba46b1181af84</t>
@@ -8209,7 +8481,11 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
-      <c r="AO41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="2" t="inlineStr"/>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
@@ -8253,10 +8529,22 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
-      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -8676,28 +8964,32 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -8737,7 +9029,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -8746,7 +9038,11 @@
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr"/>
-      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>6462a9c8d30d40b8a5e598b631170e33</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
           <t>70de38ceffd0c04fa0c4d780</t>
@@ -8767,7 +9063,11 @@
       <c r="AL44" s="2" t="inlineStr"/>
       <c r="AM44" s="2" t="inlineStr"/>
       <c r="AN44" s="2" t="inlineStr"/>
-      <c r="AO44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP44" s="2" t="inlineStr"/>
       <c r="AQ44" s="2" t="inlineStr"/>
       <c r="AR44" s="2" t="inlineStr"/>
@@ -8803,10 +9103,22 @@
         </is>
       </c>
       <c r="BH44" s="2" t="inlineStr"/>
-      <c r="BI44" s="2" t="inlineStr"/>
+      <c r="BI44" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ44" s="2" t="inlineStr"/>
-      <c r="BK44" s="2" t="inlineStr"/>
-      <c r="BL44" s="2" t="inlineStr"/>
+      <c r="BK44" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8842,28 +9154,32 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -8903,7 +9219,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -8912,7 +9228,11 @@
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr"/>
-      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>12f632c2e33e4862b3b132891593b4e5</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>f2738532e9d9abed71c17c90</t>
@@ -8933,7 +9253,11 @@
       <c r="AL45" s="2" t="inlineStr"/>
       <c r="AM45" s="2" t="inlineStr"/>
       <c r="AN45" s="2" t="inlineStr"/>
-      <c r="AO45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP45" s="2" t="inlineStr"/>
       <c r="AQ45" s="2" t="inlineStr"/>
       <c r="AR45" s="2" t="inlineStr"/>
@@ -8977,10 +9301,22 @@
         </is>
       </c>
       <c r="BH45" s="2" t="inlineStr"/>
-      <c r="BI45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ45" s="2" t="inlineStr"/>
-      <c r="BK45" s="2" t="inlineStr"/>
-      <c r="BL45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9016,28 +9352,32 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -9077,7 +9417,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -9086,7 +9426,11 @@
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr"/>
-      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>89d6fad553574859a319dab44fd792a9</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>483a678c0d747d1ca9235fb1</t>
@@ -9107,7 +9451,11 @@
       <c r="AL46" s="2" t="inlineStr"/>
       <c r="AM46" s="2" t="inlineStr"/>
       <c r="AN46" s="2" t="inlineStr"/>
-      <c r="AO46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP46" s="2" t="inlineStr"/>
       <c r="AQ46" s="2" t="inlineStr"/>
       <c r="AR46" s="2" t="inlineStr"/>
@@ -9151,10 +9499,22 @@
         </is>
       </c>
       <c r="BH46" s="2" t="inlineStr"/>
-      <c r="BI46" s="2" t="inlineStr"/>
+      <c r="BI46" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ46" s="2" t="inlineStr"/>
-      <c r="BK46" s="2" t="inlineStr"/>
-      <c r="BL46" s="2" t="inlineStr"/>
+      <c r="BK46" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -11084,7 +11444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL25"/>
+  <dimension ref="A1:BL26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13218,192 +13578,192 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02T19:28:43+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>據《彭博新聞》報導，優步將在重組過程中裁員3,300人</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Weyerhaeuser</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T21:32:00+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Homeowners who lost property in massive Highway 229 landslide sue Weyerhaeuser in federal court</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-UBER/news/</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>'-0.878</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNSUFmcTJvcXNjb0FuT1JPMUNWNU0tazdpX1h5Tm9ITWRVRXFCdmVfTUpmb1FVNnJDX19FWk80QWtTclo4SEJLdWgwNEhTUUhqaTRqZVBET1NBMEJ3OEV3S3NEdTBjb196ZjJRWTRGVWlLa3B5WV9DejFvYWFLZEZoSFIta2ZCZUhnS0Zpd3ZkemRBeGhrSWJwSUFKM1BSRXJVbU1NczZQeHcyT2xKNlE4cmI4VUp1U1BhbWMyZ2duNzdCNFY1N1FBa2NObWxvQXNudnVWSV9jaC1VTVA1bi1MWg?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>NPR for Oregonians</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>裁員</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>787032ff67084dcf996baafe88700982</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>1d8102635e3e2ec91dfc52d2</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>964f69a74bd950a753efacff</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>landslide</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>1fed1bf0b1724ebb8f24bbef97648bd6</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>8980a06dfde0c90b9e2a6380</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>fd2da2a49aa71549e38eba16</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD11" s="3" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="3" t="inlineStr"/>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr"/>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF11" s="4" t="inlineStr"/>
+      <c r="BG11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:54:08.043808+08:00</t>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
         </is>
       </c>
     </row>
@@ -13425,17 +13785,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02T19:25:48+08:00</t>
+          <t>2026-09-02T19:28:43+08:00</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Uber將裁員3300人 重組業務以精簡管理層級</t>
+          <t>據《彭博新聞》報導，優步將在重組過程中裁員3,300人</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -13481,12 +13841,12 @@
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/live/2647285</t>
+          <t>https://tw.tradingview.com/symbols/NYSE-UBER/news/</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -13513,17 +13873,17 @@
       <c r="AA12" s="3" t="inlineStr"/>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>a27407a1831242a4ac137768e2da033a</t>
+          <t>787032ff67084dcf996baafe88700982</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>9290ee9794e2e7911a3e0378</t>
+          <t>1d8102635e3e2ec91dfc52d2</t>
         </is>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>bc7256fd58df1a7a00c6c12e</t>
+          <t>964f69a74bd950a753efacff</t>
         </is>
       </c>
       <c r="AE12" s="3" t="inlineStr"/>
@@ -13548,11 +13908,7 @@
       <c r="AT12" s="3" t="inlineStr"/>
       <c r="AU12" s="3" t="inlineStr"/>
       <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW12" s="3" t="inlineStr"/>
       <c r="AX12" s="3" t="inlineStr"/>
       <c r="AY12" s="3" t="inlineStr"/>
       <c r="AZ12" s="3" t="inlineStr"/>
@@ -13564,10 +13920,14 @@
       </c>
       <c r="BC12" s="3" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr"/>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD12" s="3" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
       <c r="BE12" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
@@ -13578,13 +13938,13 @@
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
+      <c r="BG12" s="3" t="inlineStr"/>
       <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ12" s="3" t="inlineStr"/>
       <c r="BK12" s="3" t="inlineStr">
         <is>
@@ -13598,196 +13958,192 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02T17:19:25+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Meta settlement could clear the way for new AI product launches, Morgan Stanley says</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02T19:25:48+08:00</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Uber將裁員3300人 重組業務以精簡管理層級</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>0.901</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPTnlCVDJ6NTNQcnJBNVhHcEJNajZWajdBZ2cxVm42N1lPdl9mNkFWaHBqc1VNV1I0Mmp5UGRlR0p0RGZiRklBdzctQlNibDdpZ0hTamxXeHhaTG9pRVZYbHUwTGhHWFpzVEZXSG5rRkRWT3JnX3dDZVY1bUctc3M4d9IBhgFBVV95cUxPeWYyTW9TNEVVQjMtaXE3UDN5dDFEeEMtRE1QWWtaQUVHZ0JJYVlXN2NFalBSN0JUUFIzMnFpY3pFc2ZBWEhNZGNRNWctOEpyci1pZmE1NHBWMVA4bHZoZjJfVmRfOWFjWWwwSnZVM0hvR0hKRFV3cnhVVm10dFZzcS1tMUlKQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>7d4771f9a9194dc680df6d03f3559430</t>
-        </is>
-      </c>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>658639bca948a208b1608520</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>153012810f8de58e4b943c29</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2647285</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>裁員</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>a27407a1831242a4ac137768e2da033a</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>9290ee9794e2e7911a3e0378</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>bc7256fd58df1a7a00c6c12e</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC13" s="4" t="inlineStr">
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr"/>
+      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr"/>
+      <c r="AY13" s="3" t="inlineStr"/>
+      <c r="AZ13" s="3" t="inlineStr"/>
+      <c r="BA13" s="3" t="inlineStr"/>
+      <c r="BB13" s="3" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="BC13" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG13" s="4" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH13" s="4" t="inlineStr"/>
-      <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr"/>
-      <c r="BK13" s="4" t="inlineStr">
+      <c r="BD13" s="3" t="inlineStr"/>
+      <c r="BE13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG13" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
@@ -13804,22 +14160,22 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T15:54:00+08:00</t>
+          <t>2026-09-02T17:19:25+08:00</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>DOJ Probes Soaring Beef Prices at Eight Major Stores Including Walmart</t>
+          <t>Meta settlement could clear the way for new AI product launches, Morgan Stanley says</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -13830,7 +14186,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -13860,7 +14216,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>'-0.85</t>
+          <t>0.901</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr"/>
@@ -13874,12 +14230,12 @@
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZlg3Sk15d0JVV1JmNzhFX19ObzYyZzZKYUZ4TFpkRFF6YnN4T2lzYzNsdl80YXIwb21ObWdDNVdkcU5HcGNKNWZlSm5PSGw3MlJyUGI1aDhVbi1yNndwMDhhdFFDeU1Ta0h5aTJUVXMxdnJIYkJRYkYwcjQ4Y1JtQVlEWVdxZTBNU2hVNE01X3NGQTFKcVJnYjdPNjM5Q2N5WFRUR1hPYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPTnlCVDJ6NTNQcnJBNVhHcEJNajZWajdBZ2cxVm42N1lPdl9mNkFWaHBqc1VNV1I0Mmp5UGRlR0p0RGZiRklBdzctQlNibDdpZ0hTamxXeHhaTG9pRVZYbHUwTGhHWFpzVEZXSG5rRkRWT3JnX3dDZVY1bUctc3M4d9IBhgFBVV95cUxPeWYyTW9TNEVVQjMtaXE3UDN5dDFEeEMtRE1QWWtaQUVHZ0JJYVlXN2NFalBSN0JUUFIzMnFpY3pFc2ZBWEhNZGNRNWctOEpyci1pZmE1NHBWMVA4bHZoZjJfVmRfOWFjWWwwSnZVM0hvR0hKRFV3cnhVVm10dFZzcS1tMUlKQQ?oc=5</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>Newsweek</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr"/>
@@ -13890,28 +14246,28 @@
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>DOJ probe</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr">
         <is>
-          <t>50d05869400340f1b65c89f2f7d25e44</t>
+          <t>7d4771f9a9194dc680df6d03f3559430</t>
         </is>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
-          <t>60b0503c56120ce3e770ccbd</t>
+          <t>658639bca948a208b1608520</t>
         </is>
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>6a66ae2386df9bd095066f6e</t>
+          <t>153012810f8de58e4b943c29</t>
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr"/>
@@ -13947,7 +14303,7 @@
       <c r="BA14" s="4" t="inlineStr"/>
       <c r="BB14" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC14" s="4" t="inlineStr">
@@ -13958,17 +14314,17 @@
       <c r="BD14" s="4" t="inlineStr"/>
       <c r="BE14" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG14" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
@@ -13998,22 +14354,22 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T04:51:07+08:00</t>
+          <t>2026-09-02T15:54:00+08:00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Meta's $17 Billion Settlement is a Bad Deal for Teens and All Social Media Users</t>
+          <t>DOJ Probes Soaring Beef Prices at Eight Major Stores Including Walmart</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -14024,7 +14380,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -14054,7 +14410,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>'-0.953</t>
+          <t>'-0.85</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr"/>
@@ -14068,12 +14424,12 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOQ182RlJfWjJwR2VIbDdIalBibTl2ZGVjVDdzMzJWdlAxRk9XTFU3TUZ5SlhfUzl1WmF6dXNUWXpsRHVwZU52VEpxNUhkeDdJbkVFZmF5TlVfUHV0eTZWUExoelZaaXFidmpWMHZLUG5CRlAtcEF3V3lpSklEeW51QVp5c2J4SFlxcVQyUnVibWh5eUNwbjFvZ2l3Q3pLNEt6UEUyblRsTGttMG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZlg3Sk15d0JVV1JmNzhFX19ObzYyZzZKYUZ4TFpkRFF6YnN4T2lzYzNsdl80YXIwb21ObWdDNVdkcU5HcGNKNWZlSm5PSGw3MlJyUGI1aDhVbi1yNndwMDhhdFFDeU1Ta0h5aTJUVXMxdnJIYkJRYkYwcjQ4Y1JtQVlEWVdxZTBNU2hVNE01X3NGQTFKcVJnYjdPNjM5Q2N5WFRUR1hPYw?oc=5</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>Electronic Frontier Foundation</t>
+          <t>Newsweek</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr"/>
@@ -14084,28 +14440,28 @@
       </c>
       <c r="Y15" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>DOJ probe</t>
         </is>
       </c>
       <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr">
         <is>
-          <t>2a026b360f0742ab97b560e5f4b0a173</t>
+          <t>50d05869400340f1b65c89f2f7d25e44</t>
         </is>
       </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t>d85f6a468d3281f7d0a9b776</t>
+          <t>60b0503c56120ce3e770ccbd</t>
         </is>
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>610b1de09f11259ce9b2a9f2</t>
+          <t>6a66ae2386df9bd095066f6e</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr"/>
@@ -14141,7 +14497,7 @@
       <c r="BA15" s="4" t="inlineStr"/>
       <c r="BB15" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="BC15" s="4" t="inlineStr">
@@ -14152,17 +14508,17 @@
       <c r="BD15" s="4" t="inlineStr"/>
       <c r="BE15" s="4" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG15" s="4" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH15" s="4" t="inlineStr"/>
@@ -14192,22 +14548,22 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T04:41:36+08:00</t>
+          <t>2026-09-02T04:51:07+08:00</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace to Pay Over $2 Million in US Defense Contract Settlement, Shares Fall</t>
+          <t>Meta's $17 Billion Settlement is a Bad Deal for Teens and All Social Media Users</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
@@ -14248,7 +14604,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>'-0.235</t>
+          <t>'-0.953</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr"/>
@@ -14262,12 +14618,12 @@
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeVR5M0VpRGNMenItTE9fWnJsTFRMTmwybVhCclQ3YmFsOXdlWkdWN1hqMjdQZDRPWlZRcUpGNy1GRVlWM3FQdVRKSDFUbUF5NWhHSHhocUUxRU1Nb2pjVjNaN0xEMlFmX3VsZUhNZzNxY3hZbk9vQTZ0UnBoR1lpRURHUVRsWlhnSENiSWRkZVgwOWdGeHFSNlNkOVVzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOQ182RlJfWjJwR2VIbDdIalBibTl2ZGVjVDdzMzJWdlAxRk9XTFU3TUZ5SlhfUzl1WmF6dXNUWXpsRHVwZU52VEpxNUhkeDdJbkVFZmF5TlVfUHV0eTZWUExoelZaaXFidmpWMHZLUG5CRlAtcEF3V3lpSklEeW51QVp5c2J4SFlxcVQyUnVibWh5eUNwbjFvZ2l3Q3pLNEt6UEUyblRsTGttMG8?oc=5</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>moomoo.com</t>
+          <t>Electronic Frontier Foundation</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr"/>
@@ -14289,17 +14645,17 @@
       <c r="AA16" s="4" t="inlineStr"/>
       <c r="AB16" s="4" t="inlineStr">
         <is>
-          <t>d9200b4c97c8462f9dc9faf7fbda6495</t>
+          <t>2a026b360f0742ab97b560e5f4b0a173</t>
         </is>
       </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
-          <t>d44ff793e5579e7517c47329</t>
+          <t>d85f6a468d3281f7d0a9b776</t>
         </is>
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>60a684447a93ef6b014d9601</t>
+          <t>610b1de09f11259ce9b2a9f2</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr"/>
@@ -14335,7 +14691,7 @@
       <c r="BA16" s="4" t="inlineStr"/>
       <c r="BB16" s="4" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC16" s="4" t="inlineStr">
@@ -14346,17 +14702,17 @@
       <c r="BD16" s="4" t="inlineStr"/>
       <c r="BE16" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG16" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH16" s="4" t="inlineStr"/>
@@ -14386,22 +14742,22 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Honeywell Aerospace Inc.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T03:12:01+08:00</t>
+          <t>2026-09-02T04:41:36+08:00</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Attorneys General announce Meta settlement &amp; new child safety reforms for social media</t>
+          <t>Honeywell Aerospace to Pay Over $2 Million in US Defense Contract Settlement, Shares Fall</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -14442,7 +14798,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>'-0.235</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr"/>
@@ -14456,12 +14812,12 @@
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVUJoNE5mdFRfWUZKUVBqVWYyaDVZY3FNalZZVzFHbk1HYXNlbENRNjg5NlB6WnhEQlpPNV9UVWRGbXJPcWpOQWI0S3ZjVVNKb3FyZ05GOEdDNWN1dVlXM2RXb1dhR1pKSFpIQ05WQ0N0NDJZaTBFQ3VkOFpPZkJhT0p5X1J4VHFKS1NnSHQwaFhmaWtjZExqM3pVVjFxLV9pWk9tdkU5LVIzdDZMNXd4cDBzSDl3WXhDR3BZb1h6WXdQNWxaaV9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeVR5M0VpRGNMenItTE9fWnJsTFRMTmwybVhCclQ3YmFsOXdlWkdWN1hqMjdQZDRPWlZRcUpGNy1GRVlWM3FQdVRKSDFUbUF5NWhHSHhocUUxRU1Nb2pjVjNaN0xEMlFmX3VsZUhNZzNxY3hZbk9vQTZ0UnBoR1lpRURHUVRsWlhnSENiSWRkZVgwOWdGeHFSNlNkOVVzdw?oc=5</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>Morgan Messenger</t>
+          <t>moomoo.com</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr"/>
@@ -14483,17 +14839,17 @@
       <c r="AA17" s="4" t="inlineStr"/>
       <c r="AB17" s="4" t="inlineStr">
         <is>
-          <t>f8cc3fbd4749442890d61e5f530d3665</t>
+          <t>d9200b4c97c8462f9dc9faf7fbda6495</t>
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr">
         <is>
-          <t>dc6ec4e6a5e0040235847945</t>
+          <t>d44ff793e5579e7517c47329</t>
         </is>
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>7cdcd0b0254232df49e1e08e</t>
+          <t>60a684447a93ef6b014d9601</t>
         </is>
       </c>
       <c r="AE17" s="4" t="inlineStr"/>
@@ -14529,7 +14885,7 @@
       <c r="BA17" s="4" t="inlineStr"/>
       <c r="BB17" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="BC17" s="4" t="inlineStr">
@@ -14540,17 +14896,17 @@
       <c r="BD17" s="4" t="inlineStr"/>
       <c r="BE17" s="4" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG17" s="4" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH17" s="4" t="inlineStr"/>
@@ -14568,390 +14924,390 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Tyson Foods, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02T02:22:57+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Illinois lawmakers say they were blindsided by Tyson Foods layoffs</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T03:12:01+08:00</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Attorneys General announce Meta settlement &amp; new child safety reforms for social media</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>'-0.953</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>0.058</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQzVSWjBoeGtVX2lKWTQ2UVFOSmxteFdDeEl4US1naFBJazZwbTdIRWFuNDVvTnEtTG8zYkV0aFl5WDM5a2xPdVRYZVc1RUQ5SjFCbzFaWjNXREkyLVNqbU5hY29ZYWJrSVM3UEdQbTRmX0prMTdXTnIwX0syNi1mU0lkMXZRTTMzTHRhemZjZDc1c0RrOUVR?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>Quad Cities Business Journal</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>8f74cf9f2cd14e4894c3c1431869b27e</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="inlineStr">
-        <is>
-          <t>429432b682ec17a057e82c4e</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>6a6b3e93caa56075ea0653d5</t>
-        </is>
-      </c>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr">
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVUJoNE5mdFRfWUZKUVBqVWYyaDVZY3FNalZZVzFHbk1HYXNlbENRNjg5NlB6WnhEQlpPNV9UVWRGbXJPcWpOQWI0S3ZjVVNKb3FyZ05GOEdDNWN1dVlXM2RXb1dhR1pKSFpIQ05WQ0N0NDJZaTBFQ3VkOFpPZkJhT0p5X1J4VHFKS1NnSHQwaFhmaWtjZExqM3pVVjFxLV9pWk9tdkU5LVIzdDZMNXd4cDBzSDl3WXhDR3BZb1h6WXdQNWxaaV9r?oc=5</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>Morgan Messenger</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr"/>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>f8cc3fbd4749442890d61e5f530d3665</t>
+        </is>
+      </c>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>dc6ec4e6a5e0040235847945</t>
+        </is>
+      </c>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>7cdcd0b0254232df49e1e08e</t>
+        </is>
+      </c>
+      <c r="AE18" s="4" t="inlineStr"/>
+      <c r="AF18" s="4" t="inlineStr"/>
+      <c r="AG18" s="4" t="inlineStr"/>
+      <c r="AH18" s="4" t="inlineStr"/>
+      <c r="AI18" s="4" t="inlineStr"/>
+      <c r="AJ18" s="4" t="inlineStr"/>
+      <c r="AK18" s="4" t="inlineStr"/>
+      <c r="AL18" s="4" t="inlineStr"/>
+      <c r="AM18" s="4" t="inlineStr"/>
+      <c r="AN18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="BC18" s="3" t="inlineStr">
+      <c r="AP18" s="4" t="inlineStr"/>
+      <c r="AQ18" s="4" t="inlineStr"/>
+      <c r="AR18" s="4" t="inlineStr"/>
+      <c r="AS18" s="4" t="inlineStr"/>
+      <c r="AT18" s="4" t="inlineStr"/>
+      <c r="AU18" s="4" t="inlineStr"/>
+      <c r="AV18" s="4" t="inlineStr"/>
+      <c r="AW18" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX18" s="4" t="inlineStr"/>
+      <c r="AY18" s="4" t="inlineStr"/>
+      <c r="AZ18" s="4" t="inlineStr"/>
+      <c r="BA18" s="4" t="inlineStr"/>
+      <c r="BB18" s="4" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC18" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG18" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH18" s="3" t="inlineStr"/>
-      <c r="BI18" s="3" t="inlineStr"/>
-      <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr">
+      <c r="BD18" s="4" t="inlineStr"/>
+      <c r="BE18" s="4" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG18" s="4" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:54:08.043808+08:00</t>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>INTU</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Intuit Inc.</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-02T02:17:43+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Portnoy Law Firm Announces Class Action on Behalf of Intuit, Inc. Investors</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>TSN</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Tyson Foods, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02T02:22:57+08:00</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Illinois lawmakers say they were blindsided by Tyson Foods layoffs</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>'-0.693</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>'-0.953</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNMUdYaHFvSDVTSzZpM1lCd3hvUDNKMk1yQTBDamlmRWVKOXpQNHJ3djZyRWRibllPSy10VThfRjM5cDlEbWJ5VVNkU0Yxa2dXZjBGTnJOQldUd21fd2x0TEVXZ3dOSTJiOHFNSzBMS1BNR2szbzBmZ05DejZ1eGRSS010aWMxOTI5RE9ldkR2YVBuc0tDNkxDZThfbTlVYUcyR0w0d09zSDBTUEVUV3RUc19lTmNLbjV1ckRzZVdoOFlYZDRydEdhSTRlakJCSERkNUoyQ2x2WVJPU05sTGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr">
-        <is>
-          <t>e761d55596494ed5acc92f7ccad960d9</t>
-        </is>
-      </c>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>1b9304bde74454df77789d2a</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>0904304e4d6a4d9ea1e94806</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQzVSWjBoeGtVX2lKWTQ2UVFOSmxteFdDeEl4US1naFBJazZwbTdIRWFuNDVvTnEtTG8zYkV0aFl5WDM5a2xPdVRYZVc1RUQ5SjFCbzFaWjNXREkyLVNqbU5hY29ZYWJrSVM3UEdQbTRmX0prMTdXTnIwX0syNi1mU0lkMXZRTTMzTHRhemZjZDc1c0RrOUVR?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Quad Cities Business Journal</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>8f74cf9f2cd14e4894c3c1431869b27e</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>429432b682ec17a057e82c4e</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>6a6b3e93caa56075ea0653d5</t>
+        </is>
+      </c>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
-        <is>
-          <t>INTU</t>
-        </is>
-      </c>
-      <c r="BC19" s="4" t="inlineStr">
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr"/>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr"/>
+      <c r="AY19" s="3" t="inlineStr"/>
+      <c r="AZ19" s="3" t="inlineStr"/>
+      <c r="BA19" s="3" t="inlineStr"/>
+      <c r="BB19" s="3" t="inlineStr">
+        <is>
+          <t>TSN</t>
+        </is>
+      </c>
+      <c r="BC19" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG19" s="4" t="inlineStr">
+      <c r="BD19" s="3" t="inlineStr"/>
+      <c r="BE19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG19" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH19" s="4" t="inlineStr"/>
-      <c r="BI19" s="4" t="inlineStr"/>
-      <c r="BJ19" s="4" t="inlineStr"/>
-      <c r="BK19" s="4" t="inlineStr">
+      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr"/>
+      <c r="BJ19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
@@ -14968,22 +15324,22 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T01:51:17+08:00</t>
+          <t>2026-09-02T02:17:43+08:00</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>FTC alleges Amazon illegally made $20 billion by rigging billions of ad auctions</t>
+          <t>Portnoy Law Firm Announces Class Action on Behalf of Intuit, Inc. Investors</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -14994,7 +15350,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -15024,7 +15380,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>'-0.815</t>
+          <t>'-0.693</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr"/>
@@ -15038,12 +15394,12 @@
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNTG40SlVsWjA5cmh1TDRGbFNza2pqYjJZNjJfNDdKV0VkQTU5VUNGR21tWXQ5cEo4ZEVybU5aWGhLeE1MUlNkMWM4SkRjT0FiQ3BIX3hrRVZDTUh6ald1U1RPZ1V3aUZzenpDQU96X3RVUW5CZ29laldwWnRLNWNEeS1ZejMwX3l2RWVEeDEzWW1Cb25IOHM0b05nVHBSbGZFRG5BRzZiblNkbHVVd0JQNXh6Tm42WTAzd3VyRXZpSzFsUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNMUdYaHFvSDVTSzZpM1lCd3hvUDNKMk1yQTBDamlmRWVKOXpQNHJ3djZyRWRibllPSy10VThfRjM5cDlEbWJ5VVNkU0Yxa2dXZjBGTnJOQldUd21fd2x0TEVXZ3dOSTJiOHFNSzBMS1BNR2szbzBmZ05DejZ1eGRSS010aWMxOTI5RE9ldkR2YVBuc0tDNkxDZThfbTlVYUcyR0w0d09zSDBTUEVUV3RUc19lTmNLbjV1ckRzZVdoOFlYZDRydEdhSTRlakJCSERkNUoyQ2x2WVJPU05sTGc?oc=5</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>Ars Technica</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr"/>
@@ -15054,28 +15410,28 @@
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
         <is>
-          <t>FTC</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA20" s="4" t="inlineStr"/>
       <c r="AB20" s="4" t="inlineStr">
         <is>
-          <t>f7c1b97a94154e7283f2952811ece67e</t>
+          <t>e761d55596494ed5acc92f7ccad960d9</t>
         </is>
       </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
-          <t>e58beed642fdccf881f60524</t>
+          <t>1b9304bde74454df77789d2a</t>
         </is>
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>5ba73d30ec10e43eb2f1e0c8</t>
+          <t>0904304e4d6a4d9ea1e94806</t>
         </is>
       </c>
       <c r="AE20" s="4" t="inlineStr"/>
@@ -15100,14 +15456,18 @@
       <c r="AT20" s="4" t="inlineStr"/>
       <c r="AU20" s="4" t="inlineStr"/>
       <c r="AV20" s="4" t="inlineStr"/>
-      <c r="AW20" s="4" t="inlineStr"/>
+      <c r="AW20" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX20" s="4" t="inlineStr"/>
       <c r="AY20" s="4" t="inlineStr"/>
       <c r="AZ20" s="4" t="inlineStr"/>
       <c r="BA20" s="4" t="inlineStr"/>
       <c r="BB20" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="BC20" s="4" t="inlineStr">
@@ -15118,13 +15478,17 @@
       <c r="BD20" s="4" t="inlineStr"/>
       <c r="BE20" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF20" s="4" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG20" s="4" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH20" s="4" t="inlineStr"/>
@@ -15154,22 +15518,22 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:43+08:00</t>
+          <t>2026-09-02T01:51:17+08:00</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Meta’s $18 Billion Settlement: Implications for Law, Technology, and the Future of Child Safety Online</t>
+          <t>FTC alleges Amazon illegally made $20 billion by rigging billions of ad auctions</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -15180,7 +15544,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -15210,7 +15574,7 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>'-0.815</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr"/>
@@ -15224,12 +15588,12 @@
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1mcDFQQkk5VU4zZXl5Vmp5MmZMdzJYSGJmT3ZHdmxZZXU2WXRpZWFTN1JJcFNRRTZ2bkxlTmphd2c2WkQzYld4MUxEWWRoYWpsdDFMXzNJUWc3RzYzcjluc0V4cURCLUhqaUt1bE54UlB4OGNfZVVVN295bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNTG40SlVsWjA5cmh1TDRGbFNza2pqYjJZNjJfNDdKV0VkQTU5VUNGR21tWXQ5cEo4ZEVybU5aWGhLeE1MUlNkMWM4SkRjT0FiQ3BIX3hrRVZDTUh6ald1U1RPZ1V3aUZzenpDQU96X3RVUW5CZ29laldwWnRLNWNEeS1ZejMwX3l2RWVEeDEzWW1Cb25IOHM0b05nVHBSbGZFRG5BRzZiblNkbHVVd0JQNXh6Tm42WTAzd3VyRXZpSzFsUQ?oc=5</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>JD Supra</t>
+          <t>Ars Technica</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr"/>
@@ -15240,28 +15604,28 @@
       </c>
       <c r="Y21" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z21" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA21" s="4" t="inlineStr"/>
       <c r="AB21" s="4" t="inlineStr">
         <is>
-          <t>b2c5f7585da642d7bc5292f972a89181</t>
+          <t>f7c1b97a94154e7283f2952811ece67e</t>
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr">
         <is>
-          <t>11940e882df1bc9335db06f4</t>
+          <t>e58beed642fdccf881f60524</t>
         </is>
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
-          <t>c561f99ac83fafb902c78ba3</t>
+          <t>5ba73d30ec10e43eb2f1e0c8</t>
         </is>
       </c>
       <c r="AE21" s="4" t="inlineStr"/>
@@ -15286,18 +15650,14 @@
       <c r="AT21" s="4" t="inlineStr"/>
       <c r="AU21" s="4" t="inlineStr"/>
       <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW21" s="4" t="inlineStr"/>
       <c r="AX21" s="4" t="inlineStr"/>
       <c r="AY21" s="4" t="inlineStr"/>
       <c r="AZ21" s="4" t="inlineStr"/>
       <c r="BA21" s="4" t="inlineStr"/>
       <c r="BB21" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="BC21" s="4" t="inlineStr">
@@ -15308,17 +15668,13 @@
       <c r="BD21" s="4" t="inlineStr"/>
       <c r="BE21" s="4" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF21" s="4" t="inlineStr"/>
       <c r="BG21" s="4" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH21" s="4" t="inlineStr"/>
@@ -15348,22 +15704,22 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:27:00+08:00</t>
+          <t>2026-09-02T00:51:43+08:00</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Amazon Stock Extends Losses After FTC Lawsuit Over Ad Practices</t>
+          <t>Meta’s $18 Billion Settlement: Implications for Law, Technology, and the Future of Child Safety Online</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -15374,7 +15730,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -15404,7 +15760,7 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>'-0.952</t>
+          <t>0.055</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr"/>
@@ -15418,12 +15774,12 @@
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOUDZwVUpsY25wdGMtSGZCZXc4bmp2eE5raktyLTNHWGh2bnVCcERVT0hwMVFzT2ktLTk4bFpqLXh4aUF5a3Q0ektCZGhIMU1nZE1hdnRCVVQyMDVKb2hCVjJhLXAyR0xEazFvMjRjdzRLT3Z1NHRpdHJpTGdWMF84TTRhY1NxZGIwWmZBSnctYVdVeUJ3azhTag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1mcDFQQkk5VU4zZXl5Vmp5MmZMdzJYSGJmT3ZHdmxZZXU2WXRpZWFTN1JJcFNRRTZ2bkxlTmphd2c2WkQzYld4MUxEWWRoYWpsdDFMXzNJUWc3RzYzcjluc0V4cURCLUhqaUt1bE54UlB4OGNfZVVVN295bw?oc=5</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>Investor's Business Daily</t>
+          <t>JD Supra</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr"/>
@@ -15434,28 +15790,28 @@
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
         <is>
-          <t>FTC</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA22" s="4" t="inlineStr"/>
       <c r="AB22" s="4" t="inlineStr">
         <is>
-          <t>52627c58fae04b3aa7f992d2e3ea67d8</t>
+          <t>b2c5f7585da642d7bc5292f972a89181</t>
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
-          <t>ca17148438acad800895988a</t>
+          <t>11940e882df1bc9335db06f4</t>
         </is>
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>ec69b956b26f9191149ed8e8</t>
+          <t>c561f99ac83fafb902c78ba3</t>
         </is>
       </c>
       <c r="AE22" s="4" t="inlineStr"/>
@@ -15480,14 +15836,18 @@
       <c r="AT22" s="4" t="inlineStr"/>
       <c r="AU22" s="4" t="inlineStr"/>
       <c r="AV22" s="4" t="inlineStr"/>
-      <c r="AW22" s="4" t="inlineStr"/>
+      <c r="AW22" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX22" s="4" t="inlineStr"/>
       <c r="AY22" s="4" t="inlineStr"/>
       <c r="AZ22" s="4" t="inlineStr"/>
       <c r="BA22" s="4" t="inlineStr"/>
       <c r="BB22" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC22" s="4" t="inlineStr">
@@ -15498,13 +15858,17 @@
       <c r="BD22" s="4" t="inlineStr"/>
       <c r="BE22" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF22" s="4" t="inlineStr"/>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
       <c r="BG22" s="4" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH22" s="4" t="inlineStr"/>
@@ -15544,12 +15908,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:19:13+08:00</t>
+          <t>2026-09-02T00:27:00+08:00</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Jim Cramer says selling Amazon shares over new FTC lawsuit would be 'hysterical'</t>
+          <t>Amazon Stock Extends Losses After FTC Lawsuit Over Ad Practices</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -15590,7 +15954,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>'-0.673</t>
+          <t>'-0.952</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr"/>
@@ -15604,12 +15968,12 @@
       </c>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUzhUWXczbjFiZUR5RmhSdnhTZnkxWUlWUS01MHVsZnZ5T1ZkYS1Ma0RHSHlna055eVlNb0lsNG5uQzEwMHNPN1VOa2pfd092anlWN3JtOXF3YUpwajBLclFPVnJ0cFJVWllnOUN2S2Y1TEp4SzRiaGRhNWFIR0xWci1aaGxwNnpMNEZDMzlzQ3V2NWVQYzBER19WVHBkc3l5R29zT25MNGVFZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOUDZwVUpsY25wdGMtSGZCZXc4bmp2eE5raktyLTNHWGh2bnVCcERVT0hwMVFzT2ktLTk4bFpqLXh4aUF5a3Q0ektCZGhIMU1nZE1hdnRCVVQyMDVKb2hCVjJhLXAyR0xEazFvMjRjdzRLT3Z1NHRpdHJpTGdWMF84TTRhY1NxZGIwWmZBSnctYVdVeUJ3azhTag?oc=5</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Investor's Business Daily</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr"/>
@@ -15631,17 +15995,17 @@
       <c r="AA23" s="4" t="inlineStr"/>
       <c r="AB23" s="4" t="inlineStr">
         <is>
-          <t>06ceff3f53b44eeeb4bd6cd364fadf44</t>
+          <t>52627c58fae04b3aa7f992d2e3ea67d8</t>
         </is>
       </c>
       <c r="AC23" s="4" t="inlineStr">
         <is>
-          <t>bb9e834ed674d9f3215fc222</t>
+          <t>ca17148438acad800895988a</t>
         </is>
       </c>
       <c r="AD23" s="4" t="inlineStr">
         <is>
-          <t>9a0364d084bd89340cec4959</t>
+          <t>ec69b956b26f9191149ed8e8</t>
         </is>
       </c>
       <c r="AE23" s="4" t="inlineStr"/>
@@ -15720,22 +16084,22 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:00:00+08:00</t>
+          <t>2026-09-02T00:19:13+08:00</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>PNR Alert: Hagens Berman Notifies Pentair plc (NYSE: PNR) Investors of Expanded Class Period in New Securities Class Action Lawsuit and Upcoming Lead Plaintiff Deadline</t>
+          <t>Jim Cramer says selling Amazon shares over new FTC lawsuit would be 'hysterical'</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -15746,7 +16110,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -15776,7 +16140,7 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>'-0.889</t>
+          <t>'-0.673</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr"/>
@@ -15790,12 +16154,12 @@
       </c>
       <c r="U24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgJBVV95cUxQdjRwb2dzSmQxNFVfbWI1T2hFSHFNWWRqTHJldUVWQUQ2YTJSQVAzYjhhUlctY0czWEhwMnZHbjhpVFkzOW94a212RkxEalc1bFgydXVJTjNxbjh3WHdGdmcxcDdsWVNVZVNPMDFNbnpmTFNfakhYTTVRUnBmRGlIeW1LY21RTzYxbzVqLUdkQVViZkczR05Ea2RVdjcwaWpfN1hMb1djWWd6eWU2aHZhaDktcVNBalQzV283WWRIV2gyMndTeVpYN1hGQ21mTzNkUEg0QjBLUzBTQWhWQVBndXRyTEV1UmZ5bkJpdi12NjhJdnpPdXktMDUzWVczLXVvd1dtYmhHdXhJMDJTSEl0b2dOV2xLVmxpQ2Y4RWVGLW00U0Y4NnBvb014MXgzZVNTcEpGOVljeEtqbGJlSWlBdF9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUzhUWXczbjFiZUR5RmhSdnhTZnkxWUlWUS01MHVsZnZ5T1ZkYS1Ma0RHSHlna055eVlNb0lsNG5uQzEwMHNPN1VOa2pfd092anlWN3JtOXF3YUpwajBLclFPVnJ0cFJVWllnOUN2S2Y1TEp4SzRiaGRhNWFIR0xWci1aaGxwNnpMNEZDMzlzQ3V2NWVQYzBER19WVHBkc3l5R29zT25MNGVFZw?oc=5</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr"/>
@@ -15806,28 +16170,28 @@
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z24" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA24" s="4" t="inlineStr"/>
       <c r="AB24" s="4" t="inlineStr">
         <is>
-          <t>1bebc9ad98aa4d6d905996d5eaa707ac</t>
+          <t>06ceff3f53b44eeeb4bd6cd364fadf44</t>
         </is>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
-          <t>1f19476142360af8ef253668</t>
+          <t>bb9e834ed674d9f3215fc222</t>
         </is>
       </c>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t>5c5583e9fb5fd9203ad46da2</t>
+          <t>9a0364d084bd89340cec4959</t>
         </is>
       </c>
       <c r="AE24" s="4" t="inlineStr"/>
@@ -15859,7 +16223,7 @@
       <c r="BA24" s="4" t="inlineStr"/>
       <c r="BB24" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="BC24" s="4" t="inlineStr">
@@ -15906,12 +16270,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -15921,7 +16285,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Intuit Inc. Investors to Act: Class Action Filed Alleging Investor Harm</t>
+          <t>PNR Alert: Hagens Berman Notifies Pentair plc (NYSE: PNR) Investors of Expanded Class Period in New Securities Class Action Lawsuit and Upcoming Lead Plaintiff Deadline</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -15962,7 +16326,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>'-0.713</t>
+          <t>'-0.889</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr"/>
@@ -15976,12 +16340,12 @@
       </c>
       <c r="U25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxOeE12LWFkdW9kUjJ2b2lKVWxvQUxuRXlxOTBXUm00S2VSNTdaWG9UU2o3a3BvYUNlU1ZNOHM4M1ZTMnBwdWRFOXQ5SndDWFFhTjdmSjFyT3d1VFJ1V184UmEzNlF4MnZfRkhiU1Q0clNvLXdta2pMcUczMFkwZHduOFYwV3RmcDQzRHFtbEdQTk1rdTZZZlhtS2lCNHBsbmZvRUtaZlcwZUJVZ05rSTFSS01UcHZYN3ROT3JsWHhzM0RGaDZiLU1UX0hqN0J3bWYxcXQ2Mjh2bTRCVzh5UVdHR1VkTGVwblZOblR4dWNGR19pSG5kRVg5a2xXbHBVb19LLVFVOWJ0cHk0NEZuMUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgJBVV95cUxQdjRwb2dzSmQxNFVfbWI1T2hFSHFNWWRqTHJldUVWQUQ2YTJSQVAzYjhhUlctY0czWEhwMnZHbjhpVFkzOW94a212RkxEalc1bFgydXVJTjNxbjh3WHdGdmcxcDdsWVNVZVNPMDFNbnpmTFNfakhYTTVRUnBmRGlIeW1LY21RTzYxbzVqLUdkQVViZkczR05Ea2RVdjcwaWpfN1hMb1djWWd6eWU2aHZhaDktcVNBalQzV283WWRIV2gyMndTeVpYN1hGQ21mTzNkUEg0QjBLUzBTQWhWQVBndXRyTEV1UmZ5bkJpdi12NjhJdnpPdXktMDUzWVczLXVvd1dtYmhHdXhJMDJTSEl0b2dOV2xLVmxpQ2Y4RWVGLW00U0Y4NnBvb014MXgzZVNTcEpGOVljeEtqbGJlSWlBdF9n?oc=5</t>
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr"/>
@@ -16003,17 +16367,17 @@
       <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" s="4" t="inlineStr">
         <is>
-          <t>35a8656145c0472eacd68fb375e004dd</t>
+          <t>1bebc9ad98aa4d6d905996d5eaa707ac</t>
         </is>
       </c>
       <c r="AC25" s="4" t="inlineStr">
         <is>
-          <t>502f152385fec1b372a6a801</t>
+          <t>1f19476142360af8ef253668</t>
         </is>
       </c>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>aeb36e3ec38b911419731993</t>
+          <t>5c5583e9fb5fd9203ad46da2</t>
         </is>
       </c>
       <c r="AE25" s="4" t="inlineStr"/>
@@ -16038,18 +16402,14 @@
       <c r="AT25" s="4" t="inlineStr"/>
       <c r="AU25" s="4" t="inlineStr"/>
       <c r="AV25" s="4" t="inlineStr"/>
-      <c r="AW25" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW25" s="4" t="inlineStr"/>
       <c r="AX25" s="4" t="inlineStr"/>
       <c r="AY25" s="4" t="inlineStr"/>
       <c r="AZ25" s="4" t="inlineStr"/>
       <c r="BA25" s="4" t="inlineStr"/>
       <c r="BB25" s="4" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC25" s="4" t="inlineStr">
@@ -16060,17 +16420,13 @@
       <c r="BD25" s="4" t="inlineStr"/>
       <c r="BE25" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF25" s="4" t="inlineStr"/>
       <c r="BG25" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH25" s="4" t="inlineStr"/>
@@ -16087,8 +16443,202 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T00:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Intuit Inc. Investors to Act: Class Action Filed Alleging Investor Harm</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>'-0.713</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr"/>
+      <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxOeE12LWFkdW9kUjJ2b2lKVWxvQUxuRXlxOTBXUm00S2VSNTdaWG9UU2o3a3BvYUNlU1ZNOHM4M1ZTMnBwdWRFOXQ5SndDWFFhTjdmSjFyT3d1VFJ1V184UmEzNlF4MnZfRkhiU1Q0clNvLXdta2pMcUczMFkwZHduOFYwV3RmcDQzRHFtbEdQTk1rdTZZZlhtS2lCNHBsbmZvRUtaZlcwZUJVZ05rSTFSS01UcHZYN3ROT3JsWHhzM0RGaDZiLU1UX0hqN0J3bWYxcXQ2Mjh2bTRCVzh5UVdHR1VkTGVwblZOblR4dWNGR19pSG5kRVg5a2xXbHBVb19LLVFVOWJ0cHk0NEZuMUE?oc=5</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr"/>
+      <c r="X26" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y26" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA26" s="4" t="inlineStr"/>
+      <c r="AB26" s="4" t="inlineStr">
+        <is>
+          <t>35a8656145c0472eacd68fb375e004dd</t>
+        </is>
+      </c>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>502f152385fec1b372a6a801</t>
+        </is>
+      </c>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>aeb36e3ec38b911419731993</t>
+        </is>
+      </c>
+      <c r="AE26" s="4" t="inlineStr"/>
+      <c r="AF26" s="4" t="inlineStr"/>
+      <c r="AG26" s="4" t="inlineStr"/>
+      <c r="AH26" s="4" t="inlineStr"/>
+      <c r="AI26" s="4" t="inlineStr"/>
+      <c r="AJ26" s="4" t="inlineStr"/>
+      <c r="AK26" s="4" t="inlineStr"/>
+      <c r="AL26" s="4" t="inlineStr"/>
+      <c r="AM26" s="4" t="inlineStr"/>
+      <c r="AN26" s="4" t="inlineStr"/>
+      <c r="AO26" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP26" s="4" t="inlineStr"/>
+      <c r="AQ26" s="4" t="inlineStr"/>
+      <c r="AR26" s="4" t="inlineStr"/>
+      <c r="AS26" s="4" t="inlineStr"/>
+      <c r="AT26" s="4" t="inlineStr"/>
+      <c r="AU26" s="4" t="inlineStr"/>
+      <c r="AV26" s="4" t="inlineStr"/>
+      <c r="AW26" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX26" s="4" t="inlineStr"/>
+      <c r="AY26" s="4" t="inlineStr"/>
+      <c r="AZ26" s="4" t="inlineStr"/>
+      <c r="BA26" s="4" t="inlineStr"/>
+      <c r="BB26" s="4" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="BC26" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD26" s="4" t="inlineStr"/>
+      <c r="BE26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG26" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH26" s="4" t="inlineStr"/>
+      <c r="BI26" s="4" t="inlineStr"/>
+      <c r="BJ26" s="4" t="inlineStr"/>
+      <c r="BK26" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BL25"/>
+  <autoFilter ref="A1:BL26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
